--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,28 +504,28 @@
         <v>24624.65</v>
       </c>
       <c r="D2" t="n">
-        <v>24533.5</v>
+        <v>24624.65</v>
       </c>
       <c r="E2" t="n">
-        <v>91.15000000000001</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>24677.6</v>
       </c>
       <c r="G2" t="n">
-        <v>24637.91</v>
+        <v>24702.19</v>
       </c>
       <c r="H2" t="n">
-        <v>39.69</v>
+        <v>-24.59</v>
       </c>
       <c r="I2" t="n">
         <v>24497.95</v>
       </c>
       <c r="J2" t="n">
-        <v>24468.76</v>
+        <v>24522.54</v>
       </c>
       <c r="K2" t="n">
-        <v>29.19</v>
+        <v>-24.59</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -538,59 +538,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BANK NIFTY</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>57739.95</v>
-      </c>
-      <c r="D3" t="n">
-        <v>57541.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>198.15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>57931.85</v>
-      </c>
-      <c r="G3" t="n">
-        <v>57818.39</v>
-      </c>
-      <c r="H3" t="n">
-        <v>113.46</v>
-      </c>
-      <c r="I3" t="n">
-        <v>57456.35</v>
-      </c>
-      <c r="J3" t="n">
-        <v>57378.69</v>
-      </c>
-      <c r="K3" t="n">
-        <v>77.66</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>🎯 TARGET HIT</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -694,28 +642,28 @@
         <v>57739.95</v>
       </c>
       <c r="D2" t="n">
-        <v>57541.8</v>
+        <v>57739.95</v>
       </c>
       <c r="E2" t="n">
-        <v>198.15</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>57931.85</v>
       </c>
       <c r="G2" t="n">
-        <v>57818.39</v>
+        <v>57962.41</v>
       </c>
       <c r="H2" t="n">
-        <v>113.46</v>
+        <v>-30.56</v>
       </c>
       <c r="I2" t="n">
         <v>57456.35</v>
       </c>
       <c r="J2" t="n">
-        <v>57378.69</v>
+        <v>57486.91</v>
       </c>
       <c r="K2" t="n">
-        <v>77.66</v>
+        <v>-30.56</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -728,7 +676,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,6 +539,58 @@
       </c>
       <c r="N2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>24627.95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24629.4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="F3" t="n">
+        <v>24677.05</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24669.59</v>
+      </c>
+      <c r="H3" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24604.15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24596.69</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7.46</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>
@@ -552,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,6 +729,58 @@
       </c>
       <c r="N2" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>58007.95</v>
+      </c>
+      <c r="D3" t="n">
+        <v>58020.6</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-12.65</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58076.85</v>
+      </c>
+      <c r="G3" t="n">
+        <v>58160.06</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-83.20999999999999</v>
+      </c>
+      <c r="I3" t="n">
+        <v>57714.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>57797.91</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-83.20999999999999</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nifty 50" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Nifty" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Nifty 50" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Bank Nifty" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -553,44 +553,148 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24627.95</v>
+        <v>24624.65</v>
       </c>
       <c r="D3" t="n">
-        <v>24629.4</v>
+        <v>24636</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.45</v>
+        <v>-11.35</v>
       </c>
       <c r="F3" t="n">
+        <v>24677.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>24673.99</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="I3" t="n">
+        <v>24497.95</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24601.09</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-103.14</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>24636</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24570.65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="F4" t="n">
         <v>24677.05</v>
       </c>
-      <c r="G3" t="n">
-        <v>24669.59</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G4" t="n">
+        <v>24626.45</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I4" t="n">
         <v>24604.15</v>
       </c>
-      <c r="J3" t="n">
-        <v>24596.69</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.46</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="J4" t="n">
+        <v>24518.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>🎯 TARGET HIT</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0.01</v>
+      <c r="N4" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>24583.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24620.95</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24632.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="I5" t="n">
+        <v>24511.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>24522.95</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,44 +847,148 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>58007.95</v>
+        <v>57739.95</v>
       </c>
       <c r="D3" t="n">
-        <v>58020.6</v>
+        <v>58063.65</v>
       </c>
       <c r="E3" t="n">
-        <v>-12.65</v>
+        <v>-323.7</v>
       </c>
       <c r="F3" t="n">
+        <v>57931.85</v>
+      </c>
+      <c r="G3" t="n">
+        <v>58188.76</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-256.91</v>
+      </c>
+      <c r="I3" t="n">
+        <v>57456.35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>57826.61</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-370.26</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>58063.65</v>
+      </c>
+      <c r="D4" t="n">
+        <v>57746.45</v>
+      </c>
+      <c r="E4" t="n">
+        <v>317.2</v>
+      </c>
+      <c r="F4" t="n">
         <v>58076.85</v>
       </c>
-      <c r="G3" t="n">
-        <v>58160.06</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-83.20999999999999</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="G4" t="n">
+        <v>57931.75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>145.1</v>
+      </c>
+      <c r="I4" t="n">
         <v>57714.7</v>
       </c>
-      <c r="J3" t="n">
-        <v>57797.91</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-83.20999999999999</v>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="J4" t="n">
+        <v>57623.85</v>
+      </c>
+      <c r="K4" t="n">
+        <v>90.84999999999999</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>NEUTRAL</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>🎯 TARGET HIT</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>0.02</v>
+      <c r="N4" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="D5" t="n">
+        <v>57686.95</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>58015.85</v>
+      </c>
+      <c r="G5" t="n">
+        <v>57959.29</v>
+      </c>
+      <c r="H5" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="I5" t="n">
+        <v>57527.75</v>
+      </c>
+      <c r="J5" t="n">
+        <v>57471.19</v>
+      </c>
+      <c r="K5" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -657,31 +657,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>24583.8</v>
+        <v>24570.65</v>
       </c>
       <c r="D5" t="n">
         <v>24583.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-13.15</v>
       </c>
       <c r="F5" t="n">
-        <v>24620.95</v>
+        <v>24630.4</v>
       </c>
       <c r="G5" t="n">
         <v>24632.8</v>
       </c>
       <c r="H5" t="n">
-        <v>-11.85</v>
+        <v>-2.4</v>
       </c>
       <c r="I5" t="n">
-        <v>24511.1</v>
+        <v>24522.75</v>
       </c>
       <c r="J5" t="n">
         <v>24522.95</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.85</v>
+        <v>-0.2</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
     </row>
   </sheetData>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>57686.95</v>
+        <v>57746.45</v>
       </c>
       <c r="D5" t="n">
         <v>57686.95</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>59.5</v>
       </c>
       <c r="F5" t="n">
-        <v>58015.85</v>
+        <v>57994.45</v>
       </c>
       <c r="G5" t="n">
         <v>57959.29</v>
       </c>
       <c r="H5" t="n">
-        <v>56.56</v>
+        <v>35.16</v>
       </c>
       <c r="I5" t="n">
-        <v>57527.75</v>
+        <v>57686.55</v>
       </c>
       <c r="J5" t="n">
         <v>57471.19</v>
       </c>
       <c r="K5" t="n">
-        <v>56.56</v>
+        <v>215.36</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -695,6 +695,58 @@
       </c>
       <c r="N5" t="n">
         <v>0.05</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24471.7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>24576.85</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24555.95</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>24429.25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24408.35</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -989,6 +1041,58 @@
       </c>
       <c r="N5" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="D6" t="n">
+        <v>57446.25</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>57607.25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>57649.64</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-42.39</v>
+      </c>
+      <c r="I6" t="n">
+        <v>57158.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>57200.49</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-42.39</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -709,31 +709,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24471.7</v>
+        <v>24583.8</v>
       </c>
       <c r="D6" t="n">
         <v>24471.7</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>112.1</v>
       </c>
       <c r="F6" t="n">
-        <v>24576.85</v>
+        <v>24620.95</v>
       </c>
       <c r="G6" t="n">
         <v>24555.95</v>
       </c>
       <c r="H6" t="n">
-        <v>20.9</v>
+        <v>65</v>
       </c>
       <c r="I6" t="n">
-        <v>24429.25</v>
+        <v>24511.1</v>
       </c>
       <c r="J6" t="n">
         <v>24408.35</v>
       </c>
       <c r="K6" t="n">
-        <v>20.9</v>
+        <v>102.75</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>
@@ -1055,31 +1055,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>57446.25</v>
+        <v>57686.95</v>
       </c>
       <c r="D6" t="n">
         <v>57446.25</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>240.7</v>
       </c>
       <c r="F6" t="n">
-        <v>57607.25</v>
+        <v>58015.85</v>
       </c>
       <c r="G6" t="n">
         <v>57649.64</v>
       </c>
       <c r="H6" t="n">
-        <v>-42.39</v>
+        <v>366.21</v>
       </c>
       <c r="I6" t="n">
-        <v>57158.1</v>
+        <v>57527.75</v>
       </c>
       <c r="J6" t="n">
         <v>57200.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-42.39</v>
+        <v>327.26</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,6 +747,58 @@
       </c>
       <c r="N6" t="n">
         <v>0.46</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="D7" t="n">
+        <v>24435.95</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>24473.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>24517.51</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-44.21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>24265.95</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24310.16</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-44.21</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -760,7 +812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1095,6 +1147,58 @@
         <v>0.42</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="D7" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>57885.85</v>
+      </c>
+      <c r="G7" t="n">
+        <v>58096.46</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-210.61</v>
+      </c>
+      <c r="I7" t="n">
+        <v>57254</v>
+      </c>
+      <c r="J7" t="n">
+        <v>57464.61</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-210.61</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -761,31 +761,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24435.95</v>
+        <v>24471.7</v>
       </c>
       <c r="D7" t="n">
         <v>24435.95</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>35.75</v>
       </c>
       <c r="F7" t="n">
-        <v>24473.3</v>
+        <v>24576.85</v>
       </c>
       <c r="G7" t="n">
         <v>24517.51</v>
       </c>
       <c r="H7" t="n">
-        <v>-44.21</v>
+        <v>59.34</v>
       </c>
       <c r="I7" t="n">
-        <v>24265.95</v>
+        <v>24429.25</v>
       </c>
       <c r="J7" t="n">
         <v>24310.16</v>
       </c>
       <c r="K7" t="n">
-        <v>-44.21</v>
+        <v>119.09</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
     </row>
   </sheetData>
@@ -1159,31 +1159,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>57885.85</v>
+        <v>57446.25</v>
       </c>
       <c r="D7" t="n">
         <v>57885.85</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-439.6</v>
       </c>
       <c r="F7" t="n">
-        <v>57885.85</v>
+        <v>57607.25</v>
       </c>
       <c r="G7" t="n">
         <v>58096.46</v>
       </c>
       <c r="H7" t="n">
-        <v>-210.61</v>
+        <v>-489.21</v>
       </c>
       <c r="I7" t="n">
-        <v>57254</v>
+        <v>57158.1</v>
       </c>
       <c r="J7" t="n">
         <v>57464.61</v>
       </c>
       <c r="K7" t="n">
-        <v>-210.61</v>
+        <v>-306.51</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,58 @@
       </c>
       <c r="N7" t="n">
         <v>0.15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="D8" t="n">
+        <v>24395.85</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>24431.6</v>
+      </c>
+      <c r="G8" t="n">
+        <v>24447.84</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="I8" t="n">
+        <v>24311.4</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24327.64</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-16.24</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -812,7 +864,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1199,6 +1251,58 @@
         <v>0.76</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="D8" t="n">
+        <v>57635.25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>57799.15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>57773.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="I8" t="n">
+        <v>57548.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>57522.85</v>
+      </c>
+      <c r="K8" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Nifty 50" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Bank Nifty" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nifty 50" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bank Nifty" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -813,31 +813,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24395.85</v>
+        <v>24435.95</v>
       </c>
       <c r="D8" t="n">
         <v>24395.85</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>40.1</v>
       </c>
       <c r="F8" t="n">
-        <v>24431.6</v>
+        <v>24473.3</v>
       </c>
       <c r="G8" t="n">
         <v>24447.84</v>
       </c>
       <c r="H8" t="n">
-        <v>-16.24</v>
+        <v>25.46</v>
       </c>
       <c r="I8" t="n">
-        <v>24311.4</v>
+        <v>24265.95</v>
       </c>
       <c r="J8" t="n">
         <v>24327.64</v>
       </c>
       <c r="K8" t="n">
-        <v>-16.24</v>
+        <v>-61.69</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
     </row>
   </sheetData>
@@ -1263,31 +1263,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>57635.25</v>
+        <v>57885.85</v>
       </c>
       <c r="D8" t="n">
         <v>57635.25</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>250.6</v>
       </c>
       <c r="F8" t="n">
-        <v>57799.15</v>
+        <v>57885.85</v>
       </c>
       <c r="G8" t="n">
         <v>57773.4</v>
       </c>
       <c r="H8" t="n">
-        <v>25.75</v>
+        <v>112.45</v>
       </c>
       <c r="I8" t="n">
-        <v>57548.6</v>
+        <v>57254</v>
       </c>
       <c r="J8" t="n">
         <v>57522.85</v>
       </c>
       <c r="K8" t="n">
-        <v>25.75</v>
+        <v>-268.85</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -851,6 +851,58 @@
       </c>
       <c r="N8" t="n">
         <v>0.16</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>24366</v>
+      </c>
+      <c r="D9" t="n">
+        <v>24366</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>24405.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24415.2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24296.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24306.8</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -864,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,6 +1355,58 @@
         <v>0.43</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>57491.1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>57681.45</v>
+      </c>
+      <c r="G9" t="n">
+        <v>57654.89</v>
+      </c>
+      <c r="H9" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="I9" t="n">
+        <v>57380.45</v>
+      </c>
+      <c r="J9" t="n">
+        <v>57353.89</v>
+      </c>
+      <c r="K9" t="n">
+        <v>26.56</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -865,31 +865,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24366</v>
+        <v>24395.85</v>
       </c>
       <c r="D9" t="n">
         <v>24366</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>29.85</v>
       </c>
       <c r="F9" t="n">
-        <v>24405.2</v>
+        <v>24431.6</v>
       </c>
       <c r="G9" t="n">
         <v>24415.2</v>
       </c>
       <c r="H9" t="n">
-        <v>-10</v>
+        <v>16.4</v>
       </c>
       <c r="I9" t="n">
-        <v>24296.8</v>
+        <v>24311.4</v>
       </c>
       <c r="J9" t="n">
         <v>24306.8</v>
       </c>
       <c r="K9" t="n">
-        <v>-10</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
     </row>
   </sheetData>
@@ -1367,31 +1367,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57491.1</v>
+        <v>57635.25</v>
       </c>
       <c r="D9" t="n">
         <v>57491.1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>144.15</v>
       </c>
       <c r="F9" t="n">
-        <v>57681.45</v>
+        <v>57799.15</v>
       </c>
       <c r="G9" t="n">
         <v>57654.89</v>
       </c>
       <c r="H9" t="n">
-        <v>26.56</v>
+        <v>144.26</v>
       </c>
       <c r="I9" t="n">
-        <v>57380.45</v>
+        <v>57548.6</v>
       </c>
       <c r="J9" t="n">
         <v>57353.89</v>
       </c>
       <c r="K9" t="n">
-        <v>26.56</v>
+        <v>194.71</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -865,31 +865,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24395.85</v>
+        <v>24366</v>
       </c>
       <c r="D9" t="n">
         <v>24366</v>
       </c>
       <c r="E9" t="n">
-        <v>29.85</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>24431.6</v>
+        <v>24405.2</v>
       </c>
       <c r="G9" t="n">
         <v>24415.2</v>
       </c>
       <c r="H9" t="n">
-        <v>16.4</v>
+        <v>-10</v>
       </c>
       <c r="I9" t="n">
-        <v>24311.4</v>
+        <v>24296.8</v>
       </c>
       <c r="J9" t="n">
         <v>24306.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4.6</v>
+        <v>-10</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1367,31 +1367,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>57635.25</v>
+        <v>57491.1</v>
       </c>
       <c r="D9" t="n">
         <v>57491.1</v>
       </c>
       <c r="E9" t="n">
-        <v>144.15</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>57799.15</v>
+        <v>57681.45</v>
       </c>
       <c r="G9" t="n">
         <v>57654.89</v>
       </c>
       <c r="H9" t="n">
-        <v>144.26</v>
+        <v>26.56</v>
       </c>
       <c r="I9" t="n">
-        <v>57548.6</v>
+        <v>57380.45</v>
       </c>
       <c r="J9" t="n">
         <v>57353.89</v>
       </c>
       <c r="K9" t="n">
-        <v>194.71</v>
+        <v>26.56</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -902,6 +902,58 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>24287.65</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24287.65</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>24360.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>24356.19</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24226.95</v>
+      </c>
+      <c r="J10" t="n">
+        <v>24223.04</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -916,7 +968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1407,6 +1459,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>57497.8</v>
+      </c>
+      <c r="D10" t="n">
+        <v>57497.8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>57757.25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>57796.84</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-39.59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>57119.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>57159.19</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-39.59</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -917,31 +917,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24287.65</v>
+        <v>24366</v>
       </c>
       <c r="D10" t="n">
         <v>24287.65</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>24360.1</v>
+        <v>24405.2</v>
       </c>
       <c r="G10" t="n">
         <v>24356.19</v>
       </c>
       <c r="H10" t="n">
-        <v>3.91</v>
+        <v>49.01</v>
       </c>
       <c r="I10" t="n">
-        <v>24226.95</v>
+        <v>24296.8</v>
       </c>
       <c r="J10" t="n">
         <v>24223.04</v>
       </c>
       <c r="K10" t="n">
-        <v>3.91</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -1471,31 +1471,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>57497.8</v>
+        <v>57491.1</v>
       </c>
       <c r="D10" t="n">
         <v>57497.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-6.7</v>
       </c>
       <c r="F10" t="n">
-        <v>57757.25</v>
+        <v>57681.45</v>
       </c>
       <c r="G10" t="n">
         <v>57796.84</v>
       </c>
       <c r="H10" t="n">
-        <v>-39.59</v>
+        <v>-115.39</v>
       </c>
       <c r="I10" t="n">
-        <v>57119.6</v>
+        <v>57380.45</v>
       </c>
       <c r="J10" t="n">
         <v>57159.19</v>
       </c>
       <c r="K10" t="n">
-        <v>-39.59</v>
+        <v>221.26</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -1508,7 +1508,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -955,6 +955,58 @@
       </c>
       <c r="N10" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>24269.65</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24231.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="I11" t="n">
+        <v>24154.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>24116.65</v>
+      </c>
+      <c r="K11" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +1020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,6 +1563,58 @@
         <v>0.01</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>57262.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>57262.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>57584.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>57492.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>57217.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>57125.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -969,31 +969,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24154.9</v>
+        <v>24287.65</v>
       </c>
       <c r="D11" t="n">
         <v>24154.9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>132.75</v>
       </c>
       <c r="F11" t="n">
-        <v>24269.65</v>
+        <v>24360.1</v>
       </c>
       <c r="G11" t="n">
         <v>24231.4</v>
       </c>
       <c r="H11" t="n">
-        <v>38.25</v>
+        <v>128.7</v>
       </c>
       <c r="I11" t="n">
-        <v>24154.9</v>
+        <v>24226.95</v>
       </c>
       <c r="J11" t="n">
         <v>24116.65</v>
       </c>
       <c r="K11" t="n">
-        <v>38.25</v>
+        <v>110.3</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -1575,31 +1575,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>57262.4</v>
+        <v>57497.8</v>
       </c>
       <c r="D11" t="n">
         <v>57262.4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>235.4</v>
       </c>
       <c r="F11" t="n">
-        <v>57584.7</v>
+        <v>57757.25</v>
       </c>
       <c r="G11" t="n">
         <v>57492.2</v>
       </c>
       <c r="H11" t="n">
-        <v>92.5</v>
+        <v>265.05</v>
       </c>
       <c r="I11" t="n">
-        <v>57217.6</v>
+        <v>57119.6</v>
       </c>
       <c r="J11" t="n">
         <v>57125.1</v>
       </c>
       <c r="K11" t="n">
-        <v>92.5</v>
+        <v>-5.5</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1007,6 +1007,58 @@
       </c>
       <c r="N11" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24078.3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>24172.85</v>
+      </c>
+      <c r="G12" t="n">
+        <v>24158.89</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="I12" t="n">
+        <v>24025.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>24011.69</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1020,7 +1072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1615,6 +1667,58 @@
         <v>0.41</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="D12" t="n">
+        <v>57239.75</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>57356.85</v>
+      </c>
+      <c r="G12" t="n">
+        <v>57397.15</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>57001.75</v>
+      </c>
+      <c r="J12" t="n">
+        <v>57042.05</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-40.3</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1021,31 +1021,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24078.3</v>
+        <v>24154.9</v>
       </c>
       <c r="D12" t="n">
         <v>24078.3</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>24172.85</v>
+        <v>24269.65</v>
       </c>
       <c r="G12" t="n">
         <v>24158.89</v>
       </c>
       <c r="H12" t="n">
-        <v>13.96</v>
+        <v>110.76</v>
       </c>
       <c r="I12" t="n">
-        <v>24025.65</v>
+        <v>24154.9</v>
       </c>
       <c r="J12" t="n">
         <v>24011.69</v>
       </c>
       <c r="K12" t="n">
-        <v>13.96</v>
+        <v>143.21</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>57239.75</v>
+        <v>57262.4</v>
       </c>
       <c r="D12" t="n">
         <v>57239.75</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="F12" t="n">
-        <v>57356.85</v>
+        <v>57584.7</v>
       </c>
       <c r="G12" t="n">
         <v>57397.15</v>
       </c>
       <c r="H12" t="n">
-        <v>-40.3</v>
+        <v>187.55</v>
       </c>
       <c r="I12" t="n">
-        <v>57001.75</v>
+        <v>57217.6</v>
       </c>
       <c r="J12" t="n">
         <v>57042.05</v>
       </c>
       <c r="K12" t="n">
-        <v>-40.3</v>
+        <v>175.55</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1059,6 +1059,58 @@
       </c>
       <c r="N12" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="D13" t="n">
+        <v>24231.85</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>24265.15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>24269.81</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="I13" t="n">
+        <v>24184.55</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24189.21</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-4.66</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1072,7 +1124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,6 +1771,58 @@
         <v>0.04</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="D13" t="n">
+        <v>57495.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>57702.95</v>
+      </c>
+      <c r="G13" t="n">
+        <v>57655.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I13" t="n">
+        <v>57431.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>57384.15</v>
+      </c>
+      <c r="K13" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24231.85</v>
+        <v>24078.3</v>
       </c>
       <c r="D13" t="n">
         <v>24231.85</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-153.55</v>
       </c>
       <c r="F13" t="n">
-        <v>24265.15</v>
+        <v>24172.85</v>
       </c>
       <c r="G13" t="n">
         <v>24269.81</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.66</v>
+        <v>-96.95999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>24184.55</v>
+        <v>24025.65</v>
       </c>
       <c r="J13" t="n">
         <v>24189.21</v>
       </c>
       <c r="K13" t="n">
-        <v>-4.66</v>
+        <v>-163.56</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
     </row>
   </sheetData>
@@ -1783,31 +1783,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>57495.9</v>
+        <v>57239.75</v>
       </c>
       <c r="D13" t="n">
         <v>57495.9</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-256.15</v>
       </c>
       <c r="F13" t="n">
-        <v>57702.95</v>
+        <v>57356.85</v>
       </c>
       <c r="G13" t="n">
         <v>57655.3</v>
       </c>
       <c r="H13" t="n">
-        <v>47.65</v>
+        <v>-298.45</v>
       </c>
       <c r="I13" t="n">
-        <v>57431.8</v>
+        <v>57001.75</v>
       </c>
       <c r="J13" t="n">
         <v>57384.15</v>
       </c>
       <c r="K13" t="n">
-        <v>47.65</v>
+        <v>-382.4</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1111,6 +1111,58 @@
       </c>
       <c r="N13" t="n">
         <v>0.63</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>24252</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24252</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>24284.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24288.44</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="I14" t="n">
+        <v>24206.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>24211.19</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1124,7 +1176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1823,6 +1875,58 @@
         <v>0.45</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="D14" t="n">
+        <v>57761.95</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>57772.45</v>
+      </c>
+      <c r="G14" t="n">
+        <v>57862.41</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-89.95999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>57481.55</v>
+      </c>
+      <c r="J14" t="n">
+        <v>57571.51</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-89.95999999999999</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1125,31 +1125,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24252</v>
+        <v>24231.85</v>
       </c>
       <c r="D14" t="n">
         <v>24252</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-20.15</v>
       </c>
       <c r="F14" t="n">
-        <v>24284.05</v>
+        <v>24265.15</v>
       </c>
       <c r="G14" t="n">
         <v>24288.44</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.39</v>
+        <v>-23.29</v>
       </c>
       <c r="I14" t="n">
-        <v>24206.8</v>
+        <v>24184.55</v>
       </c>
       <c r="J14" t="n">
         <v>24211.19</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.39</v>
+        <v>-26.64</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -1887,31 +1887,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57761.95</v>
+        <v>57495.9</v>
       </c>
       <c r="D14" t="n">
         <v>57761.95</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-266.05</v>
       </c>
       <c r="F14" t="n">
-        <v>57772.45</v>
+        <v>57702.95</v>
       </c>
       <c r="G14" t="n">
         <v>57862.41</v>
       </c>
       <c r="H14" t="n">
-        <v>-89.95999999999999</v>
+        <v>-159.46</v>
       </c>
       <c r="I14" t="n">
-        <v>57481.55</v>
+        <v>57431.8</v>
       </c>
       <c r="J14" t="n">
         <v>57571.51</v>
       </c>
       <c r="K14" t="n">
-        <v>-89.95999999999999</v>
+        <v>-139.71</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1125,31 +1125,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24231.85</v>
+        <v>24252</v>
       </c>
       <c r="D14" t="n">
         <v>24252</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.15</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>24265.15</v>
+        <v>24284.05</v>
       </c>
       <c r="G14" t="n">
         <v>24288.44</v>
       </c>
       <c r="H14" t="n">
-        <v>-23.29</v>
+        <v>-4.39</v>
       </c>
       <c r="I14" t="n">
-        <v>24184.55</v>
+        <v>24206.8</v>
       </c>
       <c r="J14" t="n">
         <v>24211.19</v>
       </c>
       <c r="K14" t="n">
-        <v>-26.64</v>
+        <v>-4.39</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1887,31 +1887,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>57495.9</v>
+        <v>57761.95</v>
       </c>
       <c r="D14" t="n">
         <v>57761.95</v>
       </c>
       <c r="E14" t="n">
-        <v>-266.05</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>57702.95</v>
+        <v>57772.45</v>
       </c>
       <c r="G14" t="n">
         <v>57862.41</v>
       </c>
       <c r="H14" t="n">
-        <v>-159.46</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>57431.8</v>
+        <v>57481.55</v>
       </c>
       <c r="J14" t="n">
         <v>57571.51</v>
       </c>
       <c r="K14" t="n">
-        <v>-139.71</v>
+        <v>-89.95999999999999</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1162,6 +1162,58 @@
         </is>
       </c>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24219.05</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>24313</v>
+      </c>
+      <c r="G15" t="n">
+        <v>24306.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I15" t="n">
+        <v>24144.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>24137.9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1176,7 +1228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1927,6 +1979,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="D15" t="n">
+        <v>57525.95</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>57873.75</v>
+      </c>
+      <c r="G15" t="n">
+        <v>57851.15</v>
+      </c>
+      <c r="H15" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>57245.95</v>
+      </c>
+      <c r="J15" t="n">
+        <v>57223.35</v>
+      </c>
+      <c r="K15" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1177,31 +1177,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24219.05</v>
+        <v>24252</v>
       </c>
       <c r="D15" t="n">
         <v>24219.05</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>32.95</v>
       </c>
       <c r="F15" t="n">
-        <v>24313</v>
+        <v>24284.05</v>
       </c>
       <c r="G15" t="n">
         <v>24306.6</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4</v>
+        <v>-22.55</v>
       </c>
       <c r="I15" t="n">
-        <v>24144.3</v>
+        <v>24206.8</v>
       </c>
       <c r="J15" t="n">
         <v>24137.9</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -1991,31 +1991,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>57525.95</v>
+        <v>57761.95</v>
       </c>
       <c r="D15" t="n">
         <v>57525.95</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
       <c r="F15" t="n">
-        <v>57873.75</v>
+        <v>57772.45</v>
       </c>
       <c r="G15" t="n">
         <v>57851.15</v>
       </c>
       <c r="H15" t="n">
-        <v>22.6</v>
+        <v>-78.7</v>
       </c>
       <c r="I15" t="n">
-        <v>57245.95</v>
+        <v>57481.55</v>
       </c>
       <c r="J15" t="n">
         <v>57223.35</v>
       </c>
       <c r="K15" t="n">
-        <v>22.6</v>
+        <v>258.2</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1215,6 +1215,58 @@
       </c>
       <c r="N15" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="D16" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>24334.55</v>
+      </c>
+      <c r="G16" t="n">
+        <v>24407.59</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-73.04000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>24115.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>24188.49</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-73.04000000000001</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1228,7 +1280,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2031,6 +2083,58 @@
         <v>0.41</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>57514.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>57653.85</v>
+      </c>
+      <c r="G16" t="n">
+        <v>57701.61</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-47.76</v>
+      </c>
+      <c r="I16" t="n">
+        <v>57231.25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>57279.01</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-47.76</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1229,31 +1229,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24334.55</v>
+        <v>24219.05</v>
       </c>
       <c r="D16" t="n">
         <v>24334.55</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-115.5</v>
       </c>
       <c r="F16" t="n">
-        <v>24334.55</v>
+        <v>24313</v>
       </c>
       <c r="G16" t="n">
         <v>24407.59</v>
       </c>
       <c r="H16" t="n">
-        <v>-73.04000000000001</v>
+        <v>-94.59</v>
       </c>
       <c r="I16" t="n">
-        <v>24115.45</v>
+        <v>24144.3</v>
       </c>
       <c r="J16" t="n">
         <v>24188.49</v>
       </c>
       <c r="K16" t="n">
-        <v>-73.04000000000001</v>
+        <v>-44.19</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -2095,31 +2095,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>57514.2</v>
+        <v>57525.95</v>
       </c>
       <c r="D16" t="n">
         <v>57514.2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>11.75</v>
       </c>
       <c r="F16" t="n">
-        <v>57653.85</v>
+        <v>57873.75</v>
       </c>
       <c r="G16" t="n">
         <v>57701.61</v>
       </c>
       <c r="H16" t="n">
-        <v>-47.76</v>
+        <v>172.14</v>
       </c>
       <c r="I16" t="n">
-        <v>57231.25</v>
+        <v>57245.95</v>
       </c>
       <c r="J16" t="n">
         <v>57279.01</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.76</v>
+        <v>-33.06</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1267,6 +1267,58 @@
       </c>
       <c r="N16" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>24378.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>24321.65</v>
+      </c>
+      <c r="H17" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>24150.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1280,7 +1332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2135,6 +2187,58 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>57996.05</v>
+      </c>
+      <c r="G17" t="n">
+        <v>57982.59</v>
+      </c>
+      <c r="H17" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="I17" t="n">
+        <v>57611.85</v>
+      </c>
+      <c r="J17" t="n">
+        <v>57598.39</v>
+      </c>
+      <c r="K17" t="n">
+        <v>13.46</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1281,31 +1281,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24207.75</v>
+        <v>24334.55</v>
       </c>
       <c r="D17" t="n">
         <v>24207.75</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>126.8</v>
       </c>
       <c r="F17" t="n">
-        <v>24378.6</v>
+        <v>24334.55</v>
       </c>
       <c r="G17" t="n">
         <v>24321.65</v>
       </c>
       <c r="H17" t="n">
-        <v>56.95</v>
+        <v>12.9</v>
       </c>
       <c r="I17" t="n">
-        <v>24207.75</v>
+        <v>24115.45</v>
       </c>
       <c r="J17" t="n">
         <v>24150.8</v>
       </c>
       <c r="K17" t="n">
-        <v>56.95</v>
+        <v>-35.35</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -2199,31 +2199,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>57783.75</v>
+        <v>57514.2</v>
       </c>
       <c r="D17" t="n">
         <v>57783.75</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-269.55</v>
       </c>
       <c r="F17" t="n">
-        <v>57996.05</v>
+        <v>57653.85</v>
       </c>
       <c r="G17" t="n">
         <v>57982.59</v>
       </c>
       <c r="H17" t="n">
-        <v>13.46</v>
+        <v>-328.74</v>
       </c>
       <c r="I17" t="n">
-        <v>57611.85</v>
+        <v>57231.25</v>
       </c>
       <c r="J17" t="n">
         <v>57598.39</v>
       </c>
       <c r="K17" t="n">
-        <v>13.46</v>
+        <v>-367.14</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1319,6 +1319,58 @@
       </c>
       <c r="N17" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24090.85</v>
+      </c>
+      <c r="E18" t="n">
+        <v>116.9</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24378.6</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24228.59</v>
+      </c>
+      <c r="H18" t="n">
+        <v>150.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>24207.75</v>
+      </c>
+      <c r="J18" t="n">
+        <v>24021.99</v>
+      </c>
+      <c r="K18" t="n">
+        <v>185.76</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -1332,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2239,6 +2291,58 @@
         <v>0.47</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>57783.75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>57509.95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>273.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>57996.05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>57844.91</v>
+      </c>
+      <c r="H18" t="n">
+        <v>151.14</v>
+      </c>
+      <c r="I18" t="n">
+        <v>57611.85</v>
+      </c>
+      <c r="J18" t="n">
+        <v>57342.46</v>
+      </c>
+      <c r="K18" t="n">
+        <v>269.39</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1333,31 +1333,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24207.75</v>
+        <v>24122.6</v>
       </c>
       <c r="D18" t="n">
         <v>24090.85</v>
       </c>
       <c r="E18" t="n">
-        <v>116.9</v>
+        <v>31.75</v>
       </c>
       <c r="F18" t="n">
-        <v>24378.6</v>
+        <v>24122.6</v>
       </c>
       <c r="G18" t="n">
         <v>24228.59</v>
       </c>
       <c r="H18" t="n">
-        <v>150.01</v>
+        <v>-105.99</v>
       </c>
       <c r="I18" t="n">
-        <v>24207.75</v>
+        <v>24122.6</v>
       </c>
       <c r="J18" t="n">
         <v>24021.99</v>
       </c>
       <c r="K18" t="n">
-        <v>185.76</v>
+        <v>100.61</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.49</v>
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -2303,31 +2303,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57783.75</v>
+        <v>57429.75</v>
       </c>
       <c r="D18" t="n">
         <v>57509.95</v>
       </c>
       <c r="E18" t="n">
-        <v>273.8</v>
+        <v>-80.2</v>
       </c>
       <c r="F18" t="n">
-        <v>57996.05</v>
+        <v>57429.75</v>
       </c>
       <c r="G18" t="n">
         <v>57844.91</v>
       </c>
       <c r="H18" t="n">
-        <v>151.14</v>
+        <v>-415.16</v>
       </c>
       <c r="I18" t="n">
-        <v>57611.85</v>
+        <v>57429.75</v>
       </c>
       <c r="J18" t="n">
         <v>57342.46</v>
       </c>
       <c r="K18" t="n">
-        <v>269.39</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2340,7 +2340,7 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1371,6 +1371,58 @@
       </c>
       <c r="N18" t="n">
         <v>0.13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>24090.85</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24175.65</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-84.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>24297.45</v>
+      </c>
+      <c r="G19" t="n">
+        <v>24217.01</v>
+      </c>
+      <c r="H19" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="I19" t="n">
+        <v>24090.85</v>
+      </c>
+      <c r="J19" t="n">
+        <v>24105.56</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-14.71</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0.35</v>
       </c>
     </row>
   </sheetData>
@@ -1384,7 +1436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2343,6 +2395,58 @@
         <v>0.14</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>57509.95</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57496.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F19" t="n">
+        <v>58012.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>57640.46</v>
+      </c>
+      <c r="H19" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="I19" t="n">
+        <v>57509.95</v>
+      </c>
+      <c r="J19" t="n">
+        <v>57308.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>201.89</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1324,7 +1324,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1333,31 +1333,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24122.6</v>
+        <v>24090.85</v>
       </c>
       <c r="D18" t="n">
+        <v>24175.65</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-84.8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>24297.45</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24217.01</v>
+      </c>
+      <c r="H18" t="n">
+        <v>80.44</v>
+      </c>
+      <c r="I18" t="n">
         <v>24090.85</v>
       </c>
-      <c r="E18" t="n">
-        <v>31.75</v>
-      </c>
-      <c r="F18" t="n">
-        <v>24122.6</v>
-      </c>
-      <c r="G18" t="n">
-        <v>24228.59</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-105.99</v>
-      </c>
-      <c r="I18" t="n">
-        <v>24122.6</v>
-      </c>
       <c r="J18" t="n">
-        <v>24021.99</v>
+        <v>24105.56</v>
       </c>
       <c r="K18" t="n">
-        <v>100.61</v>
+        <v>-14.71</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.13</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1385,31 +1385,31 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>24175.65</v>
+      </c>
+      <c r="D19" t="n">
         <v>24090.85</v>
       </c>
-      <c r="D19" t="n">
-        <v>24175.65</v>
-      </c>
       <c r="E19" t="n">
-        <v>-84.8</v>
+        <v>84.8</v>
       </c>
       <c r="F19" t="n">
-        <v>24297.45</v>
+        <v>24188.3</v>
       </c>
       <c r="G19" t="n">
-        <v>24217.01</v>
+        <v>24228.59</v>
       </c>
       <c r="H19" t="n">
-        <v>80.44</v>
+        <v>-40.29</v>
       </c>
       <c r="I19" t="n">
-        <v>24090.85</v>
+        <v>24076.85</v>
       </c>
       <c r="J19" t="n">
-        <v>24105.56</v>
+        <v>24021.99</v>
       </c>
       <c r="K19" t="n">
-        <v>-14.71</v>
+        <v>54.86</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2355,31 +2355,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>57429.75</v>
+        <v>57509.95</v>
       </c>
       <c r="D18" t="n">
+        <v>57496.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="F18" t="n">
+        <v>58012.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>57640.46</v>
+      </c>
+      <c r="H18" t="n">
+        <v>371.94</v>
+      </c>
+      <c r="I18" t="n">
         <v>57509.95</v>
       </c>
-      <c r="E18" t="n">
-        <v>-80.2</v>
-      </c>
-      <c r="F18" t="n">
-        <v>57429.75</v>
-      </c>
-      <c r="G18" t="n">
-        <v>57844.91</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-415.16</v>
-      </c>
-      <c r="I18" t="n">
-        <v>57429.75</v>
-      </c>
       <c r="J18" t="n">
-        <v>57342.46</v>
+        <v>57308.06</v>
       </c>
       <c r="K18" t="n">
-        <v>87.29000000000001</v>
+        <v>201.89</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -2392,13 +2392,13 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2407,31 +2407,31 @@
         </is>
       </c>
       <c r="C19" t="n">
+        <v>57496.3</v>
+      </c>
+      <c r="D19" t="n">
         <v>57509.95</v>
       </c>
-      <c r="D19" t="n">
-        <v>57496.3</v>
-      </c>
       <c r="E19" t="n">
-        <v>13.65</v>
+        <v>-13.65</v>
       </c>
       <c r="F19" t="n">
-        <v>58012.4</v>
+        <v>57596.4</v>
       </c>
       <c r="G19" t="n">
-        <v>57640.46</v>
+        <v>57844.91</v>
       </c>
       <c r="H19" t="n">
-        <v>371.94</v>
+        <v>-248.51</v>
       </c>
       <c r="I19" t="n">
-        <v>57509.95</v>
+        <v>57264</v>
       </c>
       <c r="J19" t="n">
-        <v>57308.06</v>
+        <v>57342.46</v>
       </c>
       <c r="K19" t="n">
-        <v>201.89</v>
+        <v>-78.45999999999999</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1423,6 +1423,58 @@
       </c>
       <c r="N19" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>24080.4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>24080.4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>24128.7</v>
+      </c>
+      <c r="G20" t="n">
+        <v>24141.54</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-12.84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>23993.6</v>
+      </c>
+      <c r="J20" t="n">
+        <v>24006.44</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-12.84</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1436,7 +1488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2447,6 +2499,58 @@
         <v>0.02</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>58024.95</v>
+      </c>
+      <c r="D20" t="n">
+        <v>58024.95</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>58024.95</v>
+      </c>
+      <c r="G20" t="n">
+        <v>58304.15</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-279.2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>57187.35</v>
+      </c>
+      <c r="J20" t="n">
+        <v>57466.55</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-279.2</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1437,31 +1437,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24080.4</v>
+        <v>24175.65</v>
       </c>
       <c r="D20" t="n">
         <v>24080.4</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>95.25</v>
       </c>
       <c r="F20" t="n">
-        <v>24128.7</v>
+        <v>24188.3</v>
       </c>
       <c r="G20" t="n">
         <v>24141.54</v>
       </c>
       <c r="H20" t="n">
-        <v>-12.84</v>
+        <v>46.76</v>
       </c>
       <c r="I20" t="n">
-        <v>23993.6</v>
+        <v>24076.85</v>
       </c>
       <c r="J20" t="n">
         <v>24006.44</v>
       </c>
       <c r="K20" t="n">
-        <v>-12.84</v>
+        <v>70.41</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
@@ -2511,31 +2511,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58024.95</v>
+        <v>57496.3</v>
       </c>
       <c r="D20" t="n">
         <v>58024.95</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-528.65</v>
       </c>
       <c r="F20" t="n">
-        <v>58024.95</v>
+        <v>57596.4</v>
       </c>
       <c r="G20" t="n">
         <v>58304.15</v>
       </c>
       <c r="H20" t="n">
-        <v>-279.2</v>
+        <v>-707.75</v>
       </c>
       <c r="I20" t="n">
-        <v>57187.35</v>
+        <v>57264</v>
       </c>
       <c r="J20" t="n">
         <v>57466.55</v>
       </c>
       <c r="K20" t="n">
-        <v>-279.2</v>
+        <v>-202.55</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1475,6 +1475,58 @@
       </c>
       <c r="N20" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>24055.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>24055.8</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>24143.15</v>
+      </c>
+      <c r="G21" t="n">
+        <v>24148.45</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>23952.55</v>
+      </c>
+      <c r="J21" t="n">
+        <v>23957.85</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1488,7 +1540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2551,6 +2603,58 @@
         <v>0.91</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>57409.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57409.6</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>57766.25</v>
+      </c>
+      <c r="G21" t="n">
+        <v>57733.66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="I21" t="n">
+        <v>57150.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>57118.11</v>
+      </c>
+      <c r="K21" t="n">
+        <v>32.59</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1489,31 +1489,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24055.8</v>
+        <v>24080.4</v>
       </c>
       <c r="D21" t="n">
         <v>24055.8</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="F21" t="n">
-        <v>24143.15</v>
+        <v>24128.7</v>
       </c>
       <c r="G21" t="n">
         <v>24148.45</v>
       </c>
       <c r="H21" t="n">
-        <v>-5.3</v>
+        <v>-19.75</v>
       </c>
       <c r="I21" t="n">
-        <v>23952.55</v>
+        <v>23993.6</v>
       </c>
       <c r="J21" t="n">
         <v>23957.85</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.3</v>
+        <v>35.75</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2615,31 +2615,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>57409.6</v>
+        <v>58024.95</v>
       </c>
       <c r="D21" t="n">
         <v>57409.6</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>615.35</v>
       </c>
       <c r="F21" t="n">
-        <v>57766.25</v>
+        <v>58024.95</v>
       </c>
       <c r="G21" t="n">
         <v>57733.66</v>
       </c>
       <c r="H21" t="n">
-        <v>32.59</v>
+        <v>291.29</v>
       </c>
       <c r="I21" t="n">
-        <v>57150.7</v>
+        <v>57187.35</v>
       </c>
       <c r="J21" t="n">
         <v>57118.11</v>
       </c>
       <c r="K21" t="n">
-        <v>32.59</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,6 +1527,58 @@
       </c>
       <c r="N21" t="n">
         <v>0.1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>23914.45</v>
+      </c>
+      <c r="D22" t="n">
+        <v>23914.45</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>23914.45</v>
+      </c>
+      <c r="G22" t="n">
+        <v>23957</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-42.55</v>
+      </c>
+      <c r="I22" t="n">
+        <v>23786.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>23829.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-42.55</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1540,7 +1592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,6 +2707,58 @@
         <v>1.07</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>57172</v>
+      </c>
+      <c r="D22" t="n">
+        <v>57172</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>57221.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>57321</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="I22" t="n">
+        <v>56823.2</v>
+      </c>
+      <c r="J22" t="n">
+        <v>56923.1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-99.90000000000001</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1541,31 +1541,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23914.45</v>
+        <v>24055.8</v>
       </c>
       <c r="D22" t="n">
         <v>23914.45</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>141.35</v>
       </c>
       <c r="F22" t="n">
-        <v>23914.45</v>
+        <v>24143.15</v>
       </c>
       <c r="G22" t="n">
         <v>23957</v>
       </c>
       <c r="H22" t="n">
-        <v>-42.55</v>
+        <v>186.15</v>
       </c>
       <c r="I22" t="n">
-        <v>23786.8</v>
+        <v>23952.55</v>
       </c>
       <c r="J22" t="n">
         <v>23829.35</v>
       </c>
       <c r="K22" t="n">
-        <v>-42.55</v>
+        <v>123.2</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -2719,31 +2719,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>57172</v>
+        <v>57409.6</v>
       </c>
       <c r="D22" t="n">
         <v>57172</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>237.6</v>
       </c>
       <c r="F22" t="n">
-        <v>57221.1</v>
+        <v>57766.25</v>
       </c>
       <c r="G22" t="n">
         <v>57321</v>
       </c>
       <c r="H22" t="n">
-        <v>-99.90000000000001</v>
+        <v>445.25</v>
       </c>
       <c r="I22" t="n">
-        <v>56823.2</v>
+        <v>57150.7</v>
       </c>
       <c r="J22" t="n">
         <v>56923.1</v>
       </c>
       <c r="K22" t="n">
-        <v>-99.90000000000001</v>
+        <v>227.6</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1579,6 +1579,58 @@
       </c>
       <c r="N22" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>23873.45</v>
+      </c>
+      <c r="D23" t="n">
+        <v>23873.45</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>24025.4</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23974.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="I23" t="n">
+        <v>23873.45</v>
+      </c>
+      <c r="J23" t="n">
+        <v>23822.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>50.65</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1592,7 +1644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2759,6 +2811,58 @@
         <v>0.42</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>57380.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>57380.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>57753.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>57629.26</v>
+      </c>
+      <c r="H23" t="n">
+        <v>124.34</v>
+      </c>
+      <c r="I23" t="n">
+        <v>57380.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>57256.26</v>
+      </c>
+      <c r="K23" t="n">
+        <v>124.34</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1593,31 +1593,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23873.45</v>
+        <v>23914.45</v>
       </c>
       <c r="D23" t="n">
         <v>23873.45</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F23" t="n">
-        <v>24025.4</v>
+        <v>23914.45</v>
       </c>
       <c r="G23" t="n">
         <v>23974.75</v>
       </c>
       <c r="H23" t="n">
-        <v>50.65</v>
+        <v>-60.3</v>
       </c>
       <c r="I23" t="n">
-        <v>23873.45</v>
+        <v>23786.8</v>
       </c>
       <c r="J23" t="n">
         <v>23822.8</v>
       </c>
       <c r="K23" t="n">
-        <v>50.65</v>
+        <v>-36</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
@@ -2823,31 +2823,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>57380.6</v>
+        <v>57172</v>
       </c>
       <c r="D23" t="n">
         <v>57380.6</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-208.6</v>
       </c>
       <c r="F23" t="n">
-        <v>57753.6</v>
+        <v>57221.1</v>
       </c>
       <c r="G23" t="n">
         <v>57629.26</v>
       </c>
       <c r="H23" t="n">
-        <v>124.34</v>
+        <v>-408.16</v>
       </c>
       <c r="I23" t="n">
-        <v>57380.6</v>
+        <v>56823.2</v>
       </c>
       <c r="J23" t="n">
         <v>57256.26</v>
       </c>
       <c r="K23" t="n">
-        <v>124.34</v>
+        <v>-433.06</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,6 +1631,58 @@
       </c>
       <c r="N23" t="n">
         <v>0.17</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>23897.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>23897.7</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>24005.75</v>
+      </c>
+      <c r="G24" t="n">
+        <v>23970.35</v>
+      </c>
+      <c r="H24" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>23895.85</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23860.45</v>
+      </c>
+      <c r="K24" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1644,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2863,6 +2915,58 @@
         <v>0.36</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>57369.65</v>
+      </c>
+      <c r="D24" t="n">
+        <v>57369.65</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>57677.15</v>
+      </c>
+      <c r="G24" t="n">
+        <v>57589.69</v>
+      </c>
+      <c r="H24" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="I24" t="n">
+        <v>57324.55</v>
+      </c>
+      <c r="J24" t="n">
+        <v>57237.09</v>
+      </c>
+      <c r="K24" t="n">
+        <v>87.45999999999999</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1645,31 +1645,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23897.7</v>
+        <v>23873.45</v>
       </c>
       <c r="D24" t="n">
         <v>23897.7</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>-24.25</v>
       </c>
       <c r="F24" t="n">
-        <v>24005.75</v>
+        <v>24025.4</v>
       </c>
       <c r="G24" t="n">
         <v>23970.35</v>
       </c>
       <c r="H24" t="n">
-        <v>35.4</v>
+        <v>55.05</v>
       </c>
       <c r="I24" t="n">
-        <v>23895.85</v>
+        <v>23873.45</v>
       </c>
       <c r="J24" t="n">
         <v>23860.45</v>
       </c>
       <c r="K24" t="n">
-        <v>35.4</v>
+        <v>13</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -2927,31 +2927,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57369.65</v>
+        <v>57380.6</v>
       </c>
       <c r="D24" t="n">
         <v>57369.65</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>10.95</v>
       </c>
       <c r="F24" t="n">
-        <v>57677.15</v>
+        <v>57753.6</v>
       </c>
       <c r="G24" t="n">
         <v>57589.69</v>
       </c>
       <c r="H24" t="n">
-        <v>87.45999999999999</v>
+        <v>163.91</v>
       </c>
       <c r="I24" t="n">
-        <v>57324.55</v>
+        <v>57380.6</v>
       </c>
       <c r="J24" t="n">
         <v>57237.09</v>
       </c>
       <c r="K24" t="n">
-        <v>87.45999999999999</v>
+        <v>143.51</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1645,31 +1645,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23873.45</v>
+        <v>23897.7</v>
       </c>
       <c r="D24" t="n">
         <v>23897.7</v>
       </c>
       <c r="E24" t="n">
-        <v>-24.25</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>24025.4</v>
+        <v>24005.75</v>
       </c>
       <c r="G24" t="n">
         <v>23970.35</v>
       </c>
       <c r="H24" t="n">
-        <v>55.05</v>
+        <v>35.4</v>
       </c>
       <c r="I24" t="n">
-        <v>23873.45</v>
+        <v>23895.85</v>
       </c>
       <c r="J24" t="n">
         <v>23860.45</v>
       </c>
       <c r="K24" t="n">
-        <v>13</v>
+        <v>35.4</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2927,31 +2927,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>57380.6</v>
+        <v>57369.65</v>
       </c>
       <c r="D24" t="n">
         <v>57369.65</v>
       </c>
       <c r="E24" t="n">
-        <v>10.95</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>57753.6</v>
+        <v>57677.15</v>
       </c>
       <c r="G24" t="n">
         <v>57589.69</v>
       </c>
       <c r="H24" t="n">
-        <v>163.91</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>57380.6</v>
+        <v>57324.55</v>
       </c>
       <c r="J24" t="n">
         <v>57237.09</v>
       </c>
       <c r="K24" t="n">
-        <v>143.51</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1682,6 +1682,58 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>23779.15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>23779.15</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>23890</v>
+      </c>
+      <c r="G25" t="n">
+        <v>23866.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>23737.9</v>
+      </c>
+      <c r="J25" t="n">
+        <v>23714.7</v>
+      </c>
+      <c r="K25" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1696,7 +1748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2967,6 +3019,58 @@
         <v>0</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>57088.3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>57088.3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>57426.85</v>
+      </c>
+      <c r="G25" t="n">
+        <v>57342.45</v>
+      </c>
+      <c r="H25" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>57002.95</v>
+      </c>
+      <c r="J25" t="n">
+        <v>56918.55</v>
+      </c>
+      <c r="K25" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1697,31 +1697,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23779.15</v>
+        <v>23897.7</v>
       </c>
       <c r="D25" t="n">
         <v>23779.15</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>118.55</v>
       </c>
       <c r="F25" t="n">
-        <v>23890</v>
+        <v>24005.75</v>
       </c>
       <c r="G25" t="n">
         <v>23866.8</v>
       </c>
       <c r="H25" t="n">
-        <v>23.2</v>
+        <v>138.95</v>
       </c>
       <c r="I25" t="n">
-        <v>23737.9</v>
+        <v>23895.85</v>
       </c>
       <c r="J25" t="n">
         <v>23714.7</v>
       </c>
       <c r="K25" t="n">
-        <v>23.2</v>
+        <v>181.15</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -3031,31 +3031,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>57088.3</v>
+        <v>57369.65</v>
       </c>
       <c r="D25" t="n">
         <v>57088.3</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>281.35</v>
       </c>
       <c r="F25" t="n">
-        <v>57426.85</v>
+        <v>57677.15</v>
       </c>
       <c r="G25" t="n">
         <v>57342.45</v>
       </c>
       <c r="H25" t="n">
-        <v>84.40000000000001</v>
+        <v>334.7</v>
       </c>
       <c r="I25" t="n">
-        <v>57002.95</v>
+        <v>57324.55</v>
       </c>
       <c r="J25" t="n">
         <v>56918.55</v>
       </c>
       <c r="K25" t="n">
-        <v>84.40000000000001</v>
+        <v>406</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -3068,7 +3068,7 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1735,6 +1735,58 @@
       </c>
       <c r="N25" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>23635.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>23635.1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>23758.95</v>
+      </c>
+      <c r="G26" t="n">
+        <v>23721.66</v>
+      </c>
+      <c r="H26" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="I26" t="n">
+        <v>23623.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>23585.81</v>
+      </c>
+      <c r="K26" t="n">
+        <v>37.29</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3071,6 +3123,58 @@
         <v>0.49</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>56777.55</v>
+      </c>
+      <c r="D26" t="n">
+        <v>56777.55</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>57044</v>
+      </c>
+      <c r="G26" t="n">
+        <v>56974.21</v>
+      </c>
+      <c r="H26" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>56720.45</v>
+      </c>
+      <c r="J26" t="n">
+        <v>56650.66</v>
+      </c>
+      <c r="K26" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1749,31 +1749,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23635.1</v>
+        <v>23779.15</v>
       </c>
       <c r="D26" t="n">
         <v>23635.1</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>144.05</v>
       </c>
       <c r="F26" t="n">
-        <v>23758.95</v>
+        <v>23890</v>
       </c>
       <c r="G26" t="n">
         <v>23721.66</v>
       </c>
       <c r="H26" t="n">
-        <v>37.29</v>
+        <v>168.34</v>
       </c>
       <c r="I26" t="n">
-        <v>23623.1</v>
+        <v>23737.9</v>
       </c>
       <c r="J26" t="n">
         <v>23585.81</v>
       </c>
       <c r="K26" t="n">
-        <v>37.29</v>
+        <v>152.09</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
     </row>
   </sheetData>
@@ -3135,31 +3135,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>56777.55</v>
+        <v>57088.3</v>
       </c>
       <c r="D26" t="n">
         <v>56777.55</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>310.75</v>
       </c>
       <c r="F26" t="n">
-        <v>57044</v>
+        <v>57426.85</v>
       </c>
       <c r="G26" t="n">
         <v>56974.21</v>
       </c>
       <c r="H26" t="n">
-        <v>69.79000000000001</v>
+        <v>452.64</v>
       </c>
       <c r="I26" t="n">
-        <v>56720.45</v>
+        <v>57002.95</v>
       </c>
       <c r="J26" t="n">
         <v>56650.66</v>
       </c>
       <c r="K26" t="n">
-        <v>69.79000000000001</v>
+        <v>352.29</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -3172,7 +3172,7 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1787,6 +1787,58 @@
       </c>
       <c r="N26" t="n">
         <v>0.61</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>23431.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>23431.5</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>23571.55</v>
+      </c>
+      <c r="G27" t="n">
+        <v>23524.86</v>
+      </c>
+      <c r="H27" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="I27" t="n">
+        <v>23431.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>23384.81</v>
+      </c>
+      <c r="K27" t="n">
+        <v>46.69</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1800,7 +1852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3175,6 +3227,58 @@
         <v>0.55</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>56295.55</v>
+      </c>
+      <c r="D27" t="n">
+        <v>56295.55</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>56743.05</v>
+      </c>
+      <c r="G27" t="n">
+        <v>56593.89</v>
+      </c>
+      <c r="H27" t="n">
+        <v>149.16</v>
+      </c>
+      <c r="I27" t="n">
+        <v>56295.55</v>
+      </c>
+      <c r="J27" t="n">
+        <v>56146.39</v>
+      </c>
+      <c r="K27" t="n">
+        <v>149.16</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1801,31 +1801,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23431.5</v>
+        <v>23635.1</v>
       </c>
       <c r="D27" t="n">
         <v>23431.5</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>203.6</v>
       </c>
       <c r="F27" t="n">
-        <v>23571.55</v>
+        <v>23758.95</v>
       </c>
       <c r="G27" t="n">
         <v>23524.86</v>
       </c>
       <c r="H27" t="n">
-        <v>46.69</v>
+        <v>234.09</v>
       </c>
       <c r="I27" t="n">
-        <v>23431.5</v>
+        <v>23623.1</v>
       </c>
       <c r="J27" t="n">
         <v>23384.81</v>
       </c>
       <c r="K27" t="n">
-        <v>46.69</v>
+        <v>238.29</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
     </row>
   </sheetData>
@@ -3239,31 +3239,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>56295.55</v>
+        <v>56777.55</v>
       </c>
       <c r="D27" t="n">
         <v>56295.55</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>482</v>
       </c>
       <c r="F27" t="n">
-        <v>56743.05</v>
+        <v>57044</v>
       </c>
       <c r="G27" t="n">
         <v>56593.89</v>
       </c>
       <c r="H27" t="n">
-        <v>149.16</v>
+        <v>450.11</v>
       </c>
       <c r="I27" t="n">
-        <v>56295.55</v>
+        <v>56720.45</v>
       </c>
       <c r="J27" t="n">
         <v>56146.39</v>
       </c>
       <c r="K27" t="n">
-        <v>149.16</v>
+        <v>574.0599999999999</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -3276,7 +3276,7 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1839,6 +1839,58 @@
       </c>
       <c r="N27" t="n">
         <v>0.87</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>23477.8</v>
+      </c>
+      <c r="D28" t="n">
+        <v>23477.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>23494.95</v>
+      </c>
+      <c r="G28" t="n">
+        <v>23521.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-26.85</v>
+      </c>
+      <c r="I28" t="n">
+        <v>23380.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>23406.95</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-26.85</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1852,7 +1904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3279,6 +3331,58 @@
         <v>0.86</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>56471.95</v>
+      </c>
+      <c r="D28" t="n">
+        <v>56471.95</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>56575.15</v>
+      </c>
+      <c r="G28" t="n">
+        <v>56620.79</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-45.64</v>
+      </c>
+      <c r="I28" t="n">
+        <v>56231.85</v>
+      </c>
+      <c r="J28" t="n">
+        <v>56277.49</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-45.64</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1853,31 +1853,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23477.8</v>
+        <v>23431.5</v>
       </c>
       <c r="D28" t="n">
         <v>23477.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-46.3</v>
       </c>
       <c r="F28" t="n">
-        <v>23494.95</v>
+        <v>23571.55</v>
       </c>
       <c r="G28" t="n">
         <v>23521.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-26.85</v>
+        <v>49.75</v>
       </c>
       <c r="I28" t="n">
-        <v>23380.1</v>
+        <v>23431.5</v>
       </c>
       <c r="J28" t="n">
         <v>23406.95</v>
       </c>
       <c r="K28" t="n">
-        <v>-26.85</v>
+        <v>24.55</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
@@ -3343,31 +3343,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>56471.95</v>
+        <v>56295.55</v>
       </c>
       <c r="D28" t="n">
         <v>56471.95</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>-176.4</v>
       </c>
       <c r="F28" t="n">
-        <v>56575.15</v>
+        <v>56743.05</v>
       </c>
       <c r="G28" t="n">
         <v>56620.79</v>
       </c>
       <c r="H28" t="n">
-        <v>-45.64</v>
+        <v>122.26</v>
       </c>
       <c r="I28" t="n">
-        <v>56231.85</v>
+        <v>56295.55</v>
       </c>
       <c r="J28" t="n">
         <v>56277.49</v>
       </c>
       <c r="K28" t="n">
-        <v>-45.64</v>
+        <v>18.06</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1891,6 +1891,58 @@
       </c>
       <c r="N28" t="n">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NIFTY 50</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>23398.1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>23398.1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23448.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>23487</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-38.9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>23231.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>23270.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-38.9</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1904,7 +1956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3383,6 +3435,58 @@
         <v>0.31</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BANK NIFTY</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>56606.55</v>
+      </c>
+      <c r="D29" t="n">
+        <v>56606.55</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>56645.85</v>
+      </c>
+      <c r="G29" t="n">
+        <v>56935.11</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-289.26</v>
+      </c>
+      <c r="I29" t="n">
+        <v>55699.45</v>
+      </c>
+      <c r="J29" t="n">
+        <v>55988.71</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-289.26</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NEUTRAL</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>🎯 TARGET HIT</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1905,31 +1905,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23398.1</v>
+        <v>23477.8</v>
       </c>
       <c r="D29" t="n">
         <v>23398.1</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>79.7</v>
       </c>
       <c r="F29" t="n">
-        <v>23448.1</v>
+        <v>23494.95</v>
       </c>
       <c r="G29" t="n">
         <v>23487</v>
       </c>
       <c r="H29" t="n">
-        <v>-38.9</v>
+        <v>7.95</v>
       </c>
       <c r="I29" t="n">
-        <v>23231.4</v>
+        <v>23380.1</v>
       </c>
       <c r="J29" t="n">
         <v>23270.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-38.9</v>
+        <v>109.8</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
     </row>
   </sheetData>
@@ -3447,31 +3447,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>56606.55</v>
+        <v>56471.95</v>
       </c>
       <c r="D29" t="n">
         <v>56606.55</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-134.6</v>
       </c>
       <c r="F29" t="n">
-        <v>56645.85</v>
+        <v>56575.15</v>
       </c>
       <c r="G29" t="n">
         <v>56935.11</v>
       </c>
       <c r="H29" t="n">
-        <v>-289.26</v>
+        <v>-359.96</v>
       </c>
       <c r="I29" t="n">
-        <v>55699.45</v>
+        <v>56231.85</v>
       </c>
       <c r="J29" t="n">
         <v>55988.71</v>
       </c>
       <c r="K29" t="n">
-        <v>-289.26</v>
+        <v>243.14</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/Post_Market_Indexes_Validation.xlsx
+++ b/Post_Market_Indexes_Validation.xlsx
@@ -1905,31 +1905,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23477.8</v>
+        <v>23398.1</v>
       </c>
       <c r="D29" t="n">
         <v>23398.1</v>
       </c>
       <c r="E29" t="n">
-        <v>79.7</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>23494.95</v>
+        <v>23448.1</v>
       </c>
       <c r="G29" t="n">
         <v>23487</v>
       </c>
       <c r="H29" t="n">
-        <v>7.95</v>
+        <v>-38.9</v>
       </c>
       <c r="I29" t="n">
-        <v>23380.1</v>
+        <v>23231.4</v>
       </c>
       <c r="J29" t="n">
         <v>23270.3</v>
       </c>
       <c r="K29" t="n">
-        <v>109.8</v>
+        <v>-38.9</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3447,31 +3447,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>56471.95</v>
+        <v>56606.55</v>
       </c>
       <c r="D29" t="n">
         <v>56606.55</v>
       </c>
       <c r="E29" t="n">
-        <v>-134.6</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>56575.15</v>
+        <v>56645.85</v>
       </c>
       <c r="G29" t="n">
         <v>56935.11</v>
       </c>
       <c r="H29" t="n">
-        <v>-359.96</v>
+        <v>-289.26</v>
       </c>
       <c r="I29" t="n">
-        <v>56231.85</v>
+        <v>55699.45</v>
       </c>
       <c r="J29" t="n">
         <v>55988.71</v>
       </c>
       <c r="K29" t="n">
-        <v>243.14</v>
+        <v>-289.26</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3484,7 +3484,7 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
